--- a/_700_StageList.xlsx
+++ b/_700_StageList.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\NextHorizonTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51777916-BC12-49F3-9126-93000226C231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD63B57F-527B-478A-AA9E-32D94046AA12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
+    <workbookView xWindow="8333" yWindow="2768" windowWidth="21600" windowHeight="11332" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="15">
   <si>
     <t>key</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -74,6 +74,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>crystalCount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>goldCount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>_1</t>
   </si>
   <si>
@@ -81,11 +89,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>crystalCount</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>goldCount</t>
+    <t>armorGroup</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>weaponGroup</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -500,14 +508,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F38973E-7586-4DC3-8F33-E9D8C6A60768}">
-  <dimension ref="A2:P254"/>
+  <dimension ref="A2:R254"/>
   <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="20" width="12.5625" style="4" customWidth="1"/>
     <col min="21" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -524,16 +532,16 @@
         <v>6</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>8</v>
@@ -556,8 +564,14 @@
       <c r="P2" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="Q2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="3" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -586,33 +600,39 @@
         <v>7</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A4" s="2">
         <v>7000001</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C4" s="2">
         <v>1</v>
@@ -630,10 +650,10 @@
         <v>10000</v>
       </c>
       <c r="H4" s="2">
-        <v>0</v>
+        <v>1090001</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>1100001</v>
       </c>
       <c r="J4" s="2">
         <v>0</v>
@@ -656,13 +676,19 @@
       <c r="P4" s="2">
         <v>0</v>
       </c>
+      <c r="Q4" s="2">
+        <v>0</v>
+      </c>
+      <c r="R4" s="2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A5" s="3">
         <v>7000002</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C5" s="3">
         <v>2</v>
@@ -680,10 +706,10 @@
         <v>11000</v>
       </c>
       <c r="H5" s="3">
-        <v>0</v>
+        <v>1090002</v>
       </c>
       <c r="I5" s="3">
-        <v>0</v>
+        <v>1100002</v>
       </c>
       <c r="J5" s="3">
         <v>0</v>
@@ -706,13 +732,19 @@
       <c r="P5" s="3">
         <v>0</v>
       </c>
+      <c r="Q5" s="3">
+        <v>0</v>
+      </c>
+      <c r="R5" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A6" s="2">
         <v>7000003</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C6" s="2">
         <v>3</v>
@@ -730,10 +762,10 @@
         <v>12000</v>
       </c>
       <c r="H6" s="2">
-        <v>0</v>
+        <v>1090003</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>1100003</v>
       </c>
       <c r="J6" s="2">
         <v>0</v>
@@ -756,13 +788,19 @@
       <c r="P6" s="2">
         <v>0</v>
       </c>
+      <c r="Q6" s="2">
+        <v>0</v>
+      </c>
+      <c r="R6" s="2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A7" s="3">
         <v>7000004</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C7" s="3">
         <v>4</v>
@@ -780,10 +818,10 @@
         <v>13000</v>
       </c>
       <c r="H7" s="3">
-        <v>0</v>
+        <v>1090004</v>
       </c>
       <c r="I7" s="3">
-        <v>0</v>
+        <v>1100004</v>
       </c>
       <c r="J7" s="3">
         <v>0</v>
@@ -806,13 +844,19 @@
       <c r="P7" s="3">
         <v>0</v>
       </c>
+      <c r="Q7" s="3">
+        <v>0</v>
+      </c>
+      <c r="R7" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A8" s="2">
         <v>7000005</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C8" s="2">
         <v>5</v>
@@ -830,10 +874,10 @@
         <v>14000</v>
       </c>
       <c r="H8" s="2">
-        <v>0</v>
+        <v>1090001</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>1100004</v>
       </c>
       <c r="J8" s="2">
         <v>0</v>
@@ -856,13 +900,19 @@
       <c r="P8" s="2">
         <v>0</v>
       </c>
+      <c r="Q8" s="2">
+        <v>0</v>
+      </c>
+      <c r="R8" s="2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A9" s="3">
         <v>7000006</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C9" s="3">
         <v>6</v>
@@ -880,10 +930,10 @@
         <v>15000</v>
       </c>
       <c r="H9" s="3">
-        <v>0</v>
+        <v>1090002</v>
       </c>
       <c r="I9" s="3">
-        <v>0</v>
+        <v>1100003</v>
       </c>
       <c r="J9" s="3">
         <v>0</v>
@@ -906,14 +956,20 @@
       <c r="P9" s="3">
         <v>0</v>
       </c>
+      <c r="Q9" s="3">
+        <v>0</v>
+      </c>
+      <c r="R9" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="10" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
-    <row r="11" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
-    <row r="12" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
-    <row r="13" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
-    <row r="14" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
-    <row r="15" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
-    <row r="16" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="10" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="11" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="12" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="13" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="14" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="15" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="16" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
     <row r="17" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
     <row r="18" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
     <row r="19" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
